--- a/scratch/output_test.xlsx
+++ b/scratch/output_test.xlsx
@@ -195,7 +195,7 @@
     <t>Fecha Exportación:</t>
   </si>
   <si>
-    <t>2026-06-08 05:08</t>
+    <t>2026-06-08 05:56</t>
   </si>
   <si>
     <t>Métrica de Control</t>

--- a/scratch/output_test.xlsx
+++ b/scratch/output_test.xlsx
@@ -195,7 +195,7 @@
     <t>Fecha Exportación:</t>
   </si>
   <si>
-    <t>2026-06-08 05:56</t>
+    <t>2026-06-08 06:41</t>
   </si>
   <si>
     <t>Métrica de Control</t>
